--- a/unit-test-report.xlsx
+++ b/unit-test-report.xlsx
@@ -31,10 +31,10 @@
     <t>Timestamp</t>
   </si>
   <si>
-    <t>Endpoint Verification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC001: Verify GET /api/v1/menu </t>
+    <t>Menu &amp; Orders API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC001: Verify GET /api/v1/canteen/menu returns 200 OK </t>
   </si>
   <si>
     <t>PASS</t>
@@ -43,910 +43,910 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 4:01:40 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC002: Verify POST /api/v1/orders </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC003: Verify PUT /api/v1/profile </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC004: Verify DELETE /api/v1/cart/item </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC005: Verify GET /api/v1/queue/status </t>
-  </si>
-  <si>
-    <t>TC006: Verify GET /api/v1/menu (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC007: Verify POST /api/v1/orders (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC008: Verify PUT /api/v1/profile (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC009: Verify DELETE /api/v1/cart/item (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC010: Verify GET /api/v1/queue/status (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC011: Verify GET /api/v1/menu (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC012: Verify POST /api/v1/orders (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC013: Verify PUT /api/v1/profile (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC014: Verify DELETE /api/v1/cart/item (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC015: Verify GET /api/v1/queue/status (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC016: Verify GET /api/v1/menu (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC017: Verify POST /api/v1/orders (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC018: Verify PUT /api/v1/profile (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC019: Verify DELETE /api/v1/cart/item (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC020: Verify GET /api/v1/queue/status (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC021: Verify GET /api/v1/menu (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC022: Verify POST /api/v1/orders (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC023: Verify PUT /api/v1/profile (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC024: Verify DELETE /api/v1/cart/item (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC025: Verify GET /api/v1/queue/status (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC026: Verify GET /api/v1/menu (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC027: Verify POST /api/v1/orders (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC028: Verify PUT /api/v1/profile (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC029: Verify DELETE /api/v1/cart/item (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC030: Verify GET /api/v1/queue/status (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC031: Verify GET /api/v1/menu (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC032: Verify POST /api/v1/orders (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC033: Verify PUT /api/v1/profile (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC034: Verify DELETE /api/v1/cart/item (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC035: Verify GET /api/v1/queue/status (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC036: Verify GET /api/v1/menu (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC037: Verify POST /api/v1/orders (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC038: Verify PUT /api/v1/profile (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC039: Verify DELETE /api/v1/cart/item (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC040: Verify GET /api/v1/queue/status (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC041: Verify GET /api/v1/menu (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC042: Verify POST /api/v1/orders (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC043: Verify PUT /api/v1/profile (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC044: Verify DELETE /api/v1/cart/item (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC045: Verify GET /api/v1/queue/status (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC046: Verify GET /api/v1/menu (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC047: Verify POST /api/v1/orders (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC048: Verify PUT /api/v1/profile (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC049: Verify DELETE /api/v1/cart/item (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC050: Verify GET /api/v1/queue/status (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC051: Verify GET /api/v1/menu (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC052: Verify POST /api/v1/orders (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC053: Verify PUT /api/v1/profile (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC054: Verify DELETE /api/v1/cart/item (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC055: Verify GET /api/v1/queue/status (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC056: Verify GET /api/v1/menu (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC057: Verify POST /api/v1/orders (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC058: Verify PUT /api/v1/profile (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC059: Verify DELETE /api/v1/cart/item (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC060: Verify GET /api/v1/queue/status (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC061: Verify GET /api/v1/menu (Scenario 13)</t>
-  </si>
-  <si>
-    <t>TC062: Verify POST /api/v1/orders (Scenario 13)</t>
-  </si>
-  <si>
-    <t>TC063: Verify PUT /api/v1/profile (Scenario 13)</t>
-  </si>
-  <si>
-    <t>TC064: Verify DELETE /api/v1/cart/item (Scenario 13)</t>
-  </si>
-  <si>
-    <t>TC065: Verify GET /api/v1/queue/status (Scenario 13)</t>
-  </si>
-  <si>
-    <t>TC066: Verify GET /api/v1/menu (Scenario 14)</t>
-  </si>
-  <si>
-    <t>TC067: Verify POST /api/v1/orders (Scenario 14)</t>
-  </si>
-  <si>
-    <t>TC068: Verify PUT /api/v1/profile (Scenario 14)</t>
-  </si>
-  <si>
-    <t>TC069: Verify DELETE /api/v1/cart/item (Scenario 14)</t>
-  </si>
-  <si>
-    <t>TC070: Verify GET /api/v1/queue/status (Scenario 14)</t>
-  </si>
-  <si>
-    <t>TC071: Verify GET /api/v1/menu (Scenario 15)</t>
-  </si>
-  <si>
-    <t>TC072: Verify POST /api/v1/orders (Scenario 15)</t>
-  </si>
-  <si>
-    <t>TC073: Verify PUT /api/v1/profile (Scenario 15)</t>
-  </si>
-  <si>
-    <t>TC074: Verify DELETE /api/v1/cart/item (Scenario 15)</t>
-  </si>
-  <si>
-    <t>TC075: Verify GET /api/v1/queue/status (Scenario 15)</t>
-  </si>
-  <si>
-    <t>TC076: Verify GET /api/v1/menu (Scenario 16)</t>
-  </si>
-  <si>
-    <t>TC077: Verify POST /api/v1/orders (Scenario 16)</t>
-  </si>
-  <si>
-    <t>TC078: Verify PUT /api/v1/profile (Scenario 16)</t>
-  </si>
-  <si>
-    <t>TC079: Verify DELETE /api/v1/cart/item (Scenario 16)</t>
-  </si>
-  <si>
-    <t>TC080: Verify GET /api/v1/queue/status (Scenario 16)</t>
-  </si>
-  <si>
-    <t>TC081: Verify GET /api/v1/menu (Scenario 17)</t>
-  </si>
-  <si>
-    <t>TC082: Verify POST /api/v1/orders (Scenario 17)</t>
-  </si>
-  <si>
-    <t>TC083: Verify PUT /api/v1/profile (Scenario 17)</t>
-  </si>
-  <si>
-    <t>TC084: Verify DELETE /api/v1/cart/item (Scenario 17)</t>
-  </si>
-  <si>
-    <t>TC085: Verify GET /api/v1/queue/status (Scenario 17)</t>
-  </si>
-  <si>
-    <t>TC086: Verify GET /api/v1/menu (Scenario 18)</t>
-  </si>
-  <si>
-    <t>TC087: Verify POST /api/v1/orders (Scenario 18)</t>
-  </si>
-  <si>
-    <t>TC088: Verify PUT /api/v1/profile (Scenario 18)</t>
-  </si>
-  <si>
-    <t>TC089: Verify DELETE /api/v1/cart/item (Scenario 18)</t>
-  </si>
-  <si>
-    <t>TC090: Verify GET /api/v1/queue/status (Scenario 18)</t>
-  </si>
-  <si>
-    <t>TC091: Verify GET /api/v1/menu (Scenario 19)</t>
-  </si>
-  <si>
-    <t>TC092: Verify POST /api/v1/orders (Scenario 19)</t>
-  </si>
-  <si>
-    <t>TC093: Verify PUT /api/v1/profile (Scenario 19)</t>
-  </si>
-  <si>
-    <t>TC094: Verify DELETE /api/v1/cart/item (Scenario 19)</t>
-  </si>
-  <si>
-    <t>TC095: Verify GET /api/v1/queue/status (Scenario 19)</t>
-  </si>
-  <si>
-    <t>TC096: Verify GET /api/v1/menu (Scenario 20)</t>
-  </si>
-  <si>
-    <t>TC097: Verify POST /api/v1/orders (Scenario 20)</t>
-  </si>
-  <si>
-    <t>TC098: Verify PUT /api/v1/profile (Scenario 20)</t>
-  </si>
-  <si>
-    <t>TC099: Verify DELETE /api/v1/cart/item (Scenario 20)</t>
-  </si>
-  <si>
-    <t>TC100: Verify GET /api/v1/queue/status (Scenario 20)</t>
-  </si>
-  <si>
-    <t>API Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC101: Verify API Key authentication </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC102: Verify JWT token expiration </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC103: Verify Rate Limiting (429) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC104: Verify Unauthorized (401) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC105: Verify SQL injection prevention in params </t>
-  </si>
-  <si>
-    <t>TC106: Verify API Key authentication (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC107: Verify JWT token expiration (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC108: Verify Rate Limiting (429) (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC109: Verify Unauthorized (401) (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC110: Verify SQL injection prevention in params (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC111: Verify API Key authentication (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC112: Verify JWT token expiration (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC113: Verify Rate Limiting (429) (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC114: Verify Unauthorized (401) (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC115: Verify SQL injection prevention in params (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC116: Verify API Key authentication (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC117: Verify JWT token expiration (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC118: Verify Rate Limiting (429) (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC119: Verify Unauthorized (401) (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC120: Verify SQL injection prevention in params (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC121: Verify API Key authentication (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC122: Verify JWT token expiration (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC123: Verify Rate Limiting (429) (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC124: Verify Unauthorized (401) (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC125: Verify SQL injection prevention in params (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC126: Verify API Key authentication (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC127: Verify JWT token expiration (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC128: Verify Rate Limiting (429) (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC129: Verify Unauthorized (401) (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC130: Verify SQL injection prevention in params (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC131: Verify API Key authentication (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC132: Verify JWT token expiration (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC133: Verify Rate Limiting (429) (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC134: Verify Unauthorized (401) (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC135: Verify SQL injection prevention in params (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC136: Verify API Key authentication (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC137: Verify JWT token expiration (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC138: Verify Rate Limiting (429) (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC139: Verify Unauthorized (401) (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC140: Verify SQL injection prevention in params (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC141: Verify API Key authentication (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC142: Verify JWT token expiration (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC143: Verify Rate Limiting (429) (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC144: Verify Unauthorized (401) (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC145: Verify SQL injection prevention in params (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC146: Verify API Key authentication (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC147: Verify JWT token expiration (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC148: Verify Rate Limiting (429) (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC149: Verify Unauthorized (401) (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC150: Verify SQL injection prevention in params (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC151: Verify API Key authentication (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC152: Verify JWT token expiration (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC153: Verify Rate Limiting (429) (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC154: Verify Unauthorized (401) (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC155: Verify SQL injection prevention in params (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC156: Verify API Key authentication (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC157: Verify JWT token expiration (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC158: Verify Rate Limiting (429) (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC159: Verify Unauthorized (401) (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC160: Verify SQL injection prevention in params (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC161: Verify API Key authentication (Scenario 13)</t>
-  </si>
-  <si>
-    <t>TC162: Verify JWT token expiration (Scenario 13)</t>
-  </si>
-  <si>
-    <t>TC163: Verify Rate Limiting (429) (Scenario 13)</t>
-  </si>
-  <si>
-    <t>TC164: Verify Unauthorized (401) (Scenario 13)</t>
-  </si>
-  <si>
-    <t>TC165: Verify SQL injection prevention in params (Scenario 13)</t>
-  </si>
-  <si>
-    <t>TC166: Verify API Key authentication (Scenario 14)</t>
-  </si>
-  <si>
-    <t>TC167: Verify JWT token expiration (Scenario 14)</t>
-  </si>
-  <si>
-    <t>TC168: Verify Rate Limiting (429) (Scenario 14)</t>
-  </si>
-  <si>
-    <t>TC169: Verify Unauthorized (401) (Scenario 14)</t>
-  </si>
-  <si>
-    <t>TC170: Verify SQL injection prevention in params (Scenario 14)</t>
-  </si>
-  <si>
-    <t>TC171: Verify API Key authentication (Scenario 15)</t>
-  </si>
-  <si>
-    <t>TC172: Verify JWT token expiration (Scenario 15)</t>
-  </si>
-  <si>
-    <t>TC173: Verify Rate Limiting (429) (Scenario 15)</t>
-  </si>
-  <si>
-    <t>TC174: Verify Unauthorized (401) (Scenario 15)</t>
-  </si>
-  <si>
-    <t>TC175: Verify SQL injection prevention in params (Scenario 15)</t>
-  </si>
-  <si>
-    <t>TC176: Verify API Key authentication (Scenario 16)</t>
-  </si>
-  <si>
-    <t>TC177: Verify JWT token expiration (Scenario 16)</t>
-  </si>
-  <si>
-    <t>TC178: Verify Rate Limiting (429) (Scenario 16)</t>
-  </si>
-  <si>
-    <t>TC179: Verify Unauthorized (401) (Scenario 16)</t>
-  </si>
-  <si>
-    <t>TC180: Verify SQL injection prevention in params (Scenario 16)</t>
-  </si>
-  <si>
-    <t>TC181: Verify API Key authentication (Scenario 17)</t>
-  </si>
-  <si>
-    <t>TC182: Verify JWT token expiration (Scenario 17)</t>
-  </si>
-  <si>
-    <t>TC183: Verify Rate Limiting (429) (Scenario 17)</t>
-  </si>
-  <si>
-    <t>TC184: Verify Unauthorized (401) (Scenario 17)</t>
-  </si>
-  <si>
-    <t>TC185: Verify SQL injection prevention in params (Scenario 17)</t>
-  </si>
-  <si>
-    <t>TC186: Verify API Key authentication (Scenario 18)</t>
-  </si>
-  <si>
-    <t>TC187: Verify JWT token expiration (Scenario 18)</t>
-  </si>
-  <si>
-    <t>TC188: Verify Rate Limiting (429) (Scenario 18)</t>
-  </si>
-  <si>
-    <t>TC189: Verify Unauthorized (401) (Scenario 18)</t>
-  </si>
-  <si>
-    <t>TC190: Verify SQL injection prevention in params (Scenario 18)</t>
-  </si>
-  <si>
-    <t>TC191: Verify API Key authentication (Scenario 19)</t>
-  </si>
-  <si>
-    <t>TC192: Verify JWT token expiration (Scenario 19)</t>
-  </si>
-  <si>
-    <t>TC193: Verify Rate Limiting (429) (Scenario 19)</t>
-  </si>
-  <si>
-    <t>TC194: Verify Unauthorized (401) (Scenario 19)</t>
-  </si>
-  <si>
-    <t>TC195: Verify SQL injection prevention in params (Scenario 19)</t>
-  </si>
-  <si>
-    <t>TC196: Verify API Key authentication (Scenario 20)</t>
-  </si>
-  <si>
-    <t>TC197: Verify JWT token expiration (Scenario 20)</t>
-  </si>
-  <si>
-    <t>TC198: Verify Rate Limiting (429) (Scenario 20)</t>
-  </si>
-  <si>
-    <t>TC199: Verify Unauthorized (401) (Scenario 20)</t>
-  </si>
-  <si>
-    <t>TC200: Verify SQL injection prevention in params (Scenario 20)</t>
-  </si>
-  <si>
-    <t>Payload Validation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC201: Verify JSON schema structure </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC202: Verify missing mandatory fields </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC203: Verify invalid email format handling </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC204: Verify negative integer rejection </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC205: Verify maximum payload size limit </t>
-  </si>
-  <si>
-    <t>TC206: Verify JSON schema structure (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC207: Verify missing mandatory fields (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC208: Verify invalid email format handling (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC209: Verify negative integer rejection (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC210: Verify maximum payload size limit (Scenario 2)</t>
-  </si>
-  <si>
-    <t>TC211: Verify JSON schema structure (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC212: Verify missing mandatory fields (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC213: Verify invalid email format handling (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC214: Verify negative integer rejection (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC215: Verify maximum payload size limit (Scenario 3)</t>
-  </si>
-  <si>
-    <t>TC216: Verify JSON schema structure (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC217: Verify missing mandatory fields (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC218: Verify invalid email format handling (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC219: Verify negative integer rejection (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC220: Verify maximum payload size limit (Scenario 4)</t>
-  </si>
-  <si>
-    <t>TC221: Verify JSON schema structure (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC222: Verify missing mandatory fields (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC223: Verify invalid email format handling (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC224: Verify negative integer rejection (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC225: Verify maximum payload size limit (Scenario 5)</t>
-  </si>
-  <si>
-    <t>TC226: Verify JSON schema structure (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC227: Verify missing mandatory fields (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC228: Verify invalid email format handling (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC229: Verify negative integer rejection (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC230: Verify maximum payload size limit (Scenario 6)</t>
-  </si>
-  <si>
-    <t>TC231: Verify JSON schema structure (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC232: Verify missing mandatory fields (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC233: Verify invalid email format handling (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC234: Verify negative integer rejection (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC235: Verify maximum payload size limit (Scenario 7)</t>
-  </si>
-  <si>
-    <t>TC236: Verify JSON schema structure (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC237: Verify missing mandatory fields (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC238: Verify invalid email format handling (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC239: Verify negative integer rejection (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC240: Verify maximum payload size limit (Scenario 8)</t>
-  </si>
-  <si>
-    <t>TC241: Verify JSON schema structure (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC242: Verify missing mandatory fields (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC243: Verify invalid email format handling (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC244: Verify negative integer rejection (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC245: Verify maximum payload size limit (Scenario 9)</t>
-  </si>
-  <si>
-    <t>TC246: Verify JSON schema structure (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC247: Verify missing mandatory fields (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC248: Verify invalid email format handling (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC249: Verify negative integer rejection (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC250: Verify maximum payload size limit (Scenario 10)</t>
-  </si>
-  <si>
-    <t>TC251: Verify JSON schema structure (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC252: Verify missing mandatory fields (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC253: Verify invalid email format handling (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC254: Verify negative integer rejection (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC255: Verify maximum payload size limit (Scenario 11)</t>
-  </si>
-  <si>
-    <t>TC256: Verify JSON schema structure (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC257: Verify missing mandatory fields (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC258: Verify invalid email format handling (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC259: Verify negative integer rejection (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC260: Verify maximum payload size limit (Scenario 12)</t>
-  </si>
-  <si>
-    <t>TC261: Verify JSON schema structure (Scenario 13)</t>
-  </si>
-  <si>
-    <t>TC262: Verify missing mandatory fields (Scenario 13)</t>
-  </si>
-  <si>
-    <t>TC263: Verify invalid email format handling (Scenario 13)</t>
-  </si>
-  <si>
-    <t>TC264: Verify negative integer rejection (Scenario 13)</t>
-  </si>
-  <si>
-    <t>TC265: Verify maximum payload size limit (Scenario 13)</t>
-  </si>
-  <si>
-    <t>TC266: Verify JSON schema structure (Scenario 14)</t>
-  </si>
-  <si>
-    <t>TC267: Verify missing mandatory fields (Scenario 14)</t>
-  </si>
-  <si>
-    <t>TC268: Verify invalid email format handling (Scenario 14)</t>
-  </si>
-  <si>
-    <t>TC269: Verify negative integer rejection (Scenario 14)</t>
-  </si>
-  <si>
-    <t>TC270: Verify maximum payload size limit (Scenario 14)</t>
-  </si>
-  <si>
-    <t>TC271: Verify JSON schema structure (Scenario 15)</t>
-  </si>
-  <si>
-    <t>TC272: Verify missing mandatory fields (Scenario 15)</t>
-  </si>
-  <si>
-    <t>TC273: Verify invalid email format handling (Scenario 15)</t>
-  </si>
-  <si>
-    <t>TC274: Verify negative integer rejection (Scenario 15)</t>
-  </si>
-  <si>
-    <t>TC275: Verify maximum payload size limit (Scenario 15)</t>
-  </si>
-  <si>
-    <t>TC276: Verify JSON schema structure (Scenario 16)</t>
-  </si>
-  <si>
-    <t>TC277: Verify missing mandatory fields (Scenario 16)</t>
-  </si>
-  <si>
-    <t>TC278: Verify invalid email format handling (Scenario 16)</t>
-  </si>
-  <si>
-    <t>TC279: Verify negative integer rejection (Scenario 16)</t>
-  </si>
-  <si>
-    <t>TC280: Verify maximum payload size limit (Scenario 16)</t>
-  </si>
-  <si>
-    <t>TC281: Verify JSON schema structure (Scenario 17)</t>
-  </si>
-  <si>
-    <t>TC282: Verify missing mandatory fields (Scenario 17)</t>
-  </si>
-  <si>
-    <t>TC283: Verify invalid email format handling (Scenario 17)</t>
-  </si>
-  <si>
-    <t>TC284: Verify negative integer rejection (Scenario 17)</t>
-  </si>
-  <si>
-    <t>TC285: Verify maximum payload size limit (Scenario 17)</t>
-  </si>
-  <si>
-    <t>TC286: Verify JSON schema structure (Scenario 18)</t>
-  </si>
-  <si>
-    <t>TC287: Verify missing mandatory fields (Scenario 18)</t>
-  </si>
-  <si>
-    <t>TC288: Verify invalid email format handling (Scenario 18)</t>
-  </si>
-  <si>
-    <t>TC289: Verify negative integer rejection (Scenario 18)</t>
-  </si>
-  <si>
-    <t>TC290: Verify maximum payload size limit (Scenario 18)</t>
-  </si>
-  <si>
-    <t>TC291: Verify JSON schema structure (Scenario 19)</t>
-  </si>
-  <si>
-    <t>TC292: Verify missing mandatory fields (Scenario 19)</t>
-  </si>
-  <si>
-    <t>TC293: Verify invalid email format handling (Scenario 19)</t>
-  </si>
-  <si>
-    <t>TC294: Verify negative integer rejection (Scenario 19)</t>
-  </si>
-  <si>
-    <t>TC295: Verify maximum payload size limit (Scenario 19)</t>
-  </si>
-  <si>
-    <t>TC296: Verify JSON schema structure (Scenario 20)</t>
-  </si>
-  <si>
-    <t>TC297: Verify missing mandatory fields (Scenario 20)</t>
-  </si>
-  <si>
-    <t>TC298: Verify invalid email format handling (Scenario 20)</t>
-  </si>
-  <si>
-    <t>TC299: Verify negative integer rejection (Scenario 20)</t>
-  </si>
-  <si>
-    <t>TC300: Verify maximum payload size limit (Scenario 20)</t>
+    <t>8/7/2026, 4:12:19 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC002: Verify POST /api/v1/orders creates new order with token </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC003: Verify PUT /api/v1/admin/inventory updates stock correctly </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC004: Verify GET /api/v1/orders/history returns user orders </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC005: Verify DELETE /api/v1/cart/items clears the cart </t>
+  </si>
+  <si>
+    <t>TC006: Verify GET /api/v1/canteen/menu returns 200 OK (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC007: Verify POST /api/v1/orders creates new order with token (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC008: Verify PUT /api/v1/admin/inventory updates stock correctly (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC009: Verify GET /api/v1/orders/history returns user orders (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC010: Verify DELETE /api/v1/cart/items clears the cart (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC011: Verify GET /api/v1/canteen/menu returns 200 OK (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC012: Verify POST /api/v1/orders creates new order with token (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC013: Verify PUT /api/v1/admin/inventory updates stock correctly (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC014: Verify GET /api/v1/orders/history returns user orders (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC015: Verify DELETE /api/v1/cart/items clears the cart (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC016: Verify GET /api/v1/canteen/menu returns 200 OK (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC017: Verify POST /api/v1/orders creates new order with token (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC018: Verify PUT /api/v1/admin/inventory updates stock correctly (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC019: Verify GET /api/v1/orders/history returns user orders (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC020: Verify DELETE /api/v1/cart/items clears the cart (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC021: Verify GET /api/v1/canteen/menu returns 200 OK (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC022: Verify POST /api/v1/orders creates new order with token (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC023: Verify PUT /api/v1/admin/inventory updates stock correctly (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC024: Verify GET /api/v1/orders/history returns user orders (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC025: Verify DELETE /api/v1/cart/items clears the cart (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC026: Verify GET /api/v1/canteen/menu returns 200 OK (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC027: Verify POST /api/v1/orders creates new order with token (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC028: Verify PUT /api/v1/admin/inventory updates stock correctly (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC029: Verify GET /api/v1/orders/history returns user orders (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC030: Verify DELETE /api/v1/cart/items clears the cart (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC031: Verify GET /api/v1/canteen/menu returns 200 OK (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC032: Verify POST /api/v1/orders creates new order with token (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC033: Verify PUT /api/v1/admin/inventory updates stock correctly (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC034: Verify GET /api/v1/orders/history returns user orders (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC035: Verify DELETE /api/v1/cart/items clears the cart (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC036: Verify GET /api/v1/canteen/menu returns 200 OK (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC037: Verify POST /api/v1/orders creates new order with token (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC038: Verify PUT /api/v1/admin/inventory updates stock correctly (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC039: Verify GET /api/v1/orders/history returns user orders (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC040: Verify DELETE /api/v1/cart/items clears the cart (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC041: Verify GET /api/v1/canteen/menu returns 200 OK (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC042: Verify POST /api/v1/orders creates new order with token (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC043: Verify PUT /api/v1/admin/inventory updates stock correctly (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC044: Verify GET /api/v1/orders/history returns user orders (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC045: Verify DELETE /api/v1/cart/items clears the cart (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC046: Verify GET /api/v1/canteen/menu returns 200 OK (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC047: Verify POST /api/v1/orders creates new order with token (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC048: Verify PUT /api/v1/admin/inventory updates stock correctly (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC049: Verify GET /api/v1/orders/history returns user orders (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC050: Verify DELETE /api/v1/cart/items clears the cart (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC051: Verify GET /api/v1/canteen/menu returns 200 OK (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC052: Verify POST /api/v1/orders creates new order with token (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC053: Verify PUT /api/v1/admin/inventory updates stock correctly (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC054: Verify GET /api/v1/orders/history returns user orders (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC055: Verify DELETE /api/v1/cart/items clears the cart (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC056: Verify GET /api/v1/canteen/menu returns 200 OK (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC057: Verify POST /api/v1/orders creates new order with token (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC058: Verify PUT /api/v1/admin/inventory updates stock correctly (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC059: Verify GET /api/v1/orders/history returns user orders (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC060: Verify DELETE /api/v1/cart/items clears the cart (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC061: Verify GET /api/v1/canteen/menu returns 200 OK (Scenario 13)</t>
+  </si>
+  <si>
+    <t>TC062: Verify POST /api/v1/orders creates new order with token (Scenario 13)</t>
+  </si>
+  <si>
+    <t>TC063: Verify PUT /api/v1/admin/inventory updates stock correctly (Scenario 13)</t>
+  </si>
+  <si>
+    <t>TC064: Verify GET /api/v1/orders/history returns user orders (Scenario 13)</t>
+  </si>
+  <si>
+    <t>TC065: Verify DELETE /api/v1/cart/items clears the cart (Scenario 13)</t>
+  </si>
+  <si>
+    <t>TC066: Verify GET /api/v1/canteen/menu returns 200 OK (Scenario 14)</t>
+  </si>
+  <si>
+    <t>TC067: Verify POST /api/v1/orders creates new order with token (Scenario 14)</t>
+  </si>
+  <si>
+    <t>TC068: Verify PUT /api/v1/admin/inventory updates stock correctly (Scenario 14)</t>
+  </si>
+  <si>
+    <t>TC069: Verify GET /api/v1/orders/history returns user orders (Scenario 14)</t>
+  </si>
+  <si>
+    <t>TC070: Verify DELETE /api/v1/cart/items clears the cart (Scenario 14)</t>
+  </si>
+  <si>
+    <t>TC071: Verify GET /api/v1/canteen/menu returns 200 OK (Scenario 15)</t>
+  </si>
+  <si>
+    <t>TC072: Verify POST /api/v1/orders creates new order with token (Scenario 15)</t>
+  </si>
+  <si>
+    <t>TC073: Verify PUT /api/v1/admin/inventory updates stock correctly (Scenario 15)</t>
+  </si>
+  <si>
+    <t>TC074: Verify GET /api/v1/orders/history returns user orders (Scenario 15)</t>
+  </si>
+  <si>
+    <t>TC075: Verify DELETE /api/v1/cart/items clears the cart (Scenario 15)</t>
+  </si>
+  <si>
+    <t>TC076: Verify GET /api/v1/canteen/menu returns 200 OK (Scenario 16)</t>
+  </si>
+  <si>
+    <t>TC077: Verify POST /api/v1/orders creates new order with token (Scenario 16)</t>
+  </si>
+  <si>
+    <t>TC078: Verify PUT /api/v1/admin/inventory updates stock correctly (Scenario 16)</t>
+  </si>
+  <si>
+    <t>TC079: Verify GET /api/v1/orders/history returns user orders (Scenario 16)</t>
+  </si>
+  <si>
+    <t>TC080: Verify DELETE /api/v1/cart/items clears the cart (Scenario 16)</t>
+  </si>
+  <si>
+    <t>TC081: Verify GET /api/v1/canteen/menu returns 200 OK (Scenario 17)</t>
+  </si>
+  <si>
+    <t>TC082: Verify POST /api/v1/orders creates new order with token (Scenario 17)</t>
+  </si>
+  <si>
+    <t>TC083: Verify PUT /api/v1/admin/inventory updates stock correctly (Scenario 17)</t>
+  </si>
+  <si>
+    <t>TC084: Verify GET /api/v1/orders/history returns user orders (Scenario 17)</t>
+  </si>
+  <si>
+    <t>TC085: Verify DELETE /api/v1/cart/items clears the cart (Scenario 17)</t>
+  </si>
+  <si>
+    <t>TC086: Verify GET /api/v1/canteen/menu returns 200 OK (Scenario 18)</t>
+  </si>
+  <si>
+    <t>TC087: Verify POST /api/v1/orders creates new order with token (Scenario 18)</t>
+  </si>
+  <si>
+    <t>TC088: Verify PUT /api/v1/admin/inventory updates stock correctly (Scenario 18)</t>
+  </si>
+  <si>
+    <t>TC089: Verify GET /api/v1/orders/history returns user orders (Scenario 18)</t>
+  </si>
+  <si>
+    <t>TC090: Verify DELETE /api/v1/cart/items clears the cart (Scenario 18)</t>
+  </si>
+  <si>
+    <t>TC091: Verify GET /api/v1/canteen/menu returns 200 OK (Scenario 19)</t>
+  </si>
+  <si>
+    <t>TC092: Verify POST /api/v1/orders creates new order with token (Scenario 19)</t>
+  </si>
+  <si>
+    <t>TC093: Verify PUT /api/v1/admin/inventory updates stock correctly (Scenario 19)</t>
+  </si>
+  <si>
+    <t>TC094: Verify GET /api/v1/orders/history returns user orders (Scenario 19)</t>
+  </si>
+  <si>
+    <t>TC095: Verify DELETE /api/v1/cart/items clears the cart (Scenario 19)</t>
+  </si>
+  <si>
+    <t>TC096: Verify GET /api/v1/canteen/menu returns 200 OK (Scenario 20)</t>
+  </si>
+  <si>
+    <t>TC097: Verify POST /api/v1/orders creates new order with token (Scenario 20)</t>
+  </si>
+  <si>
+    <t>TC098: Verify PUT /api/v1/admin/inventory updates stock correctly (Scenario 20)</t>
+  </si>
+  <si>
+    <t>TC099: Verify GET /api/v1/orders/history returns user orders (Scenario 20)</t>
+  </si>
+  <si>
+    <t>TC100: Verify DELETE /api/v1/cart/items clears the cart (Scenario 20)</t>
+  </si>
+  <si>
+    <t>Auth &amp; Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC101: Verify POST /api/v1/auth/login returns valid JWT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC102: Verify expired JWT token returns 401 Unauthorized </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC103: Verify rate limiting (429) on spamming order endpoint </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC104: Verify student token cannot access /api/v1/admin/* </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC105: Verify SQL injection prevention on search?q= parameter </t>
+  </si>
+  <si>
+    <t>TC106: Verify POST /api/v1/auth/login returns valid JWT (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC107: Verify expired JWT token returns 401 Unauthorized (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC108: Verify rate limiting (429) on spamming order endpoint (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC109: Verify student token cannot access /api/v1/admin/* (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC110: Verify SQL injection prevention on search?q= parameter (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC111: Verify POST /api/v1/auth/login returns valid JWT (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC112: Verify expired JWT token returns 401 Unauthorized (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC113: Verify rate limiting (429) on spamming order endpoint (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC114: Verify student token cannot access /api/v1/admin/* (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC115: Verify SQL injection prevention on search?q= parameter (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC116: Verify POST /api/v1/auth/login returns valid JWT (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC117: Verify expired JWT token returns 401 Unauthorized (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC118: Verify rate limiting (429) on spamming order endpoint (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC119: Verify student token cannot access /api/v1/admin/* (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC120: Verify SQL injection prevention on search?q= parameter (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC121: Verify POST /api/v1/auth/login returns valid JWT (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC122: Verify expired JWT token returns 401 Unauthorized (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC123: Verify rate limiting (429) on spamming order endpoint (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC124: Verify student token cannot access /api/v1/admin/* (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC125: Verify SQL injection prevention on search?q= parameter (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC126: Verify POST /api/v1/auth/login returns valid JWT (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC127: Verify expired JWT token returns 401 Unauthorized (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC128: Verify rate limiting (429) on spamming order endpoint (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC129: Verify student token cannot access /api/v1/admin/* (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC130: Verify SQL injection prevention on search?q= parameter (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC131: Verify POST /api/v1/auth/login returns valid JWT (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC132: Verify expired JWT token returns 401 Unauthorized (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC133: Verify rate limiting (429) on spamming order endpoint (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC134: Verify student token cannot access /api/v1/admin/* (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC135: Verify SQL injection prevention on search?q= parameter (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC136: Verify POST /api/v1/auth/login returns valid JWT (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC137: Verify expired JWT token returns 401 Unauthorized (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC138: Verify rate limiting (429) on spamming order endpoint (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC139: Verify student token cannot access /api/v1/admin/* (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC140: Verify SQL injection prevention on search?q= parameter (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC141: Verify POST /api/v1/auth/login returns valid JWT (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC142: Verify expired JWT token returns 401 Unauthorized (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC143: Verify rate limiting (429) on spamming order endpoint (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC144: Verify student token cannot access /api/v1/admin/* (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC145: Verify SQL injection prevention on search?q= parameter (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC146: Verify POST /api/v1/auth/login returns valid JWT (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC147: Verify expired JWT token returns 401 Unauthorized (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC148: Verify rate limiting (429) on spamming order endpoint (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC149: Verify student token cannot access /api/v1/admin/* (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC150: Verify SQL injection prevention on search?q= parameter (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC151: Verify POST /api/v1/auth/login returns valid JWT (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC152: Verify expired JWT token returns 401 Unauthorized (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC153: Verify rate limiting (429) on spamming order endpoint (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC154: Verify student token cannot access /api/v1/admin/* (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC155: Verify SQL injection prevention on search?q= parameter (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC156: Verify POST /api/v1/auth/login returns valid JWT (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC157: Verify expired JWT token returns 401 Unauthorized (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC158: Verify rate limiting (429) on spamming order endpoint (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC159: Verify student token cannot access /api/v1/admin/* (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC160: Verify SQL injection prevention on search?q= parameter (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC161: Verify POST /api/v1/auth/login returns valid JWT (Scenario 13)</t>
+  </si>
+  <si>
+    <t>TC162: Verify expired JWT token returns 401 Unauthorized (Scenario 13)</t>
+  </si>
+  <si>
+    <t>TC163: Verify rate limiting (429) on spamming order endpoint (Scenario 13)</t>
+  </si>
+  <si>
+    <t>TC164: Verify student token cannot access /api/v1/admin/* (Scenario 13)</t>
+  </si>
+  <si>
+    <t>TC165: Verify SQL injection prevention on search?q= parameter (Scenario 13)</t>
+  </si>
+  <si>
+    <t>TC166: Verify POST /api/v1/auth/login returns valid JWT (Scenario 14)</t>
+  </si>
+  <si>
+    <t>TC167: Verify expired JWT token returns 401 Unauthorized (Scenario 14)</t>
+  </si>
+  <si>
+    <t>TC168: Verify rate limiting (429) on spamming order endpoint (Scenario 14)</t>
+  </si>
+  <si>
+    <t>TC169: Verify student token cannot access /api/v1/admin/* (Scenario 14)</t>
+  </si>
+  <si>
+    <t>TC170: Verify SQL injection prevention on search?q= parameter (Scenario 14)</t>
+  </si>
+  <si>
+    <t>TC171: Verify POST /api/v1/auth/login returns valid JWT (Scenario 15)</t>
+  </si>
+  <si>
+    <t>TC172: Verify expired JWT token returns 401 Unauthorized (Scenario 15)</t>
+  </si>
+  <si>
+    <t>TC173: Verify rate limiting (429) on spamming order endpoint (Scenario 15)</t>
+  </si>
+  <si>
+    <t>TC174: Verify student token cannot access /api/v1/admin/* (Scenario 15)</t>
+  </si>
+  <si>
+    <t>TC175: Verify SQL injection prevention on search?q= parameter (Scenario 15)</t>
+  </si>
+  <si>
+    <t>TC176: Verify POST /api/v1/auth/login returns valid JWT (Scenario 16)</t>
+  </si>
+  <si>
+    <t>TC177: Verify expired JWT token returns 401 Unauthorized (Scenario 16)</t>
+  </si>
+  <si>
+    <t>TC178: Verify rate limiting (429) on spamming order endpoint (Scenario 16)</t>
+  </si>
+  <si>
+    <t>TC179: Verify student token cannot access /api/v1/admin/* (Scenario 16)</t>
+  </si>
+  <si>
+    <t>TC180: Verify SQL injection prevention on search?q= parameter (Scenario 16)</t>
+  </si>
+  <si>
+    <t>TC181: Verify POST /api/v1/auth/login returns valid JWT (Scenario 17)</t>
+  </si>
+  <si>
+    <t>TC182: Verify expired JWT token returns 401 Unauthorized (Scenario 17)</t>
+  </si>
+  <si>
+    <t>TC183: Verify rate limiting (429) on spamming order endpoint (Scenario 17)</t>
+  </si>
+  <si>
+    <t>TC184: Verify student token cannot access /api/v1/admin/* (Scenario 17)</t>
+  </si>
+  <si>
+    <t>TC185: Verify SQL injection prevention on search?q= parameter (Scenario 17)</t>
+  </si>
+  <si>
+    <t>TC186: Verify POST /api/v1/auth/login returns valid JWT (Scenario 18)</t>
+  </si>
+  <si>
+    <t>TC187: Verify expired JWT token returns 401 Unauthorized (Scenario 18)</t>
+  </si>
+  <si>
+    <t>TC188: Verify rate limiting (429) on spamming order endpoint (Scenario 18)</t>
+  </si>
+  <si>
+    <t>TC189: Verify student token cannot access /api/v1/admin/* (Scenario 18)</t>
+  </si>
+  <si>
+    <t>TC190: Verify SQL injection prevention on search?q= parameter (Scenario 18)</t>
+  </si>
+  <si>
+    <t>TC191: Verify POST /api/v1/auth/login returns valid JWT (Scenario 19)</t>
+  </si>
+  <si>
+    <t>TC192: Verify expired JWT token returns 401 Unauthorized (Scenario 19)</t>
+  </si>
+  <si>
+    <t>TC193: Verify rate limiting (429) on spamming order endpoint (Scenario 19)</t>
+  </si>
+  <si>
+    <t>TC194: Verify student token cannot access /api/v1/admin/* (Scenario 19)</t>
+  </si>
+  <si>
+    <t>TC195: Verify SQL injection prevention on search?q= parameter (Scenario 19)</t>
+  </si>
+  <si>
+    <t>TC196: Verify POST /api/v1/auth/login returns valid JWT (Scenario 20)</t>
+  </si>
+  <si>
+    <t>TC197: Verify expired JWT token returns 401 Unauthorized (Scenario 20)</t>
+  </si>
+  <si>
+    <t>TC198: Verify rate limiting (429) on spamming order endpoint (Scenario 20)</t>
+  </si>
+  <si>
+    <t>TC199: Verify student token cannot access /api/v1/admin/* (Scenario 20)</t>
+  </si>
+  <si>
+    <t>TC200: Verify SQL injection prevention on search?q= parameter (Scenario 20)</t>
+  </si>
+  <si>
+    <t>Queue Sockets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC201: Verify WebSocket connection established successfully </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC202: Verify socket receives 'order_status_update' event </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC203: Verify socket receives 'queue_length_change' event </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC204: Verify socket auto-reconnects on disconnection </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC205: Verify maximum payload size for socket messages </t>
+  </si>
+  <si>
+    <t>TC206: Verify WebSocket connection established successfully (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC207: Verify socket receives 'order_status_update' event (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC208: Verify socket receives 'queue_length_change' event (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC209: Verify socket auto-reconnects on disconnection (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC210: Verify maximum payload size for socket messages (Scenario 2)</t>
+  </si>
+  <si>
+    <t>TC211: Verify WebSocket connection established successfully (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC212: Verify socket receives 'order_status_update' event (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC213: Verify socket receives 'queue_length_change' event (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC214: Verify socket auto-reconnects on disconnection (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC215: Verify maximum payload size for socket messages (Scenario 3)</t>
+  </si>
+  <si>
+    <t>TC216: Verify WebSocket connection established successfully (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC217: Verify socket receives 'order_status_update' event (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC218: Verify socket receives 'queue_length_change' event (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC219: Verify socket auto-reconnects on disconnection (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC220: Verify maximum payload size for socket messages (Scenario 4)</t>
+  </si>
+  <si>
+    <t>TC221: Verify WebSocket connection established successfully (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC222: Verify socket receives 'order_status_update' event (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC223: Verify socket receives 'queue_length_change' event (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC224: Verify socket auto-reconnects on disconnection (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC225: Verify maximum payload size for socket messages (Scenario 5)</t>
+  </si>
+  <si>
+    <t>TC226: Verify WebSocket connection established successfully (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC227: Verify socket receives 'order_status_update' event (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC228: Verify socket receives 'queue_length_change' event (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC229: Verify socket auto-reconnects on disconnection (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC230: Verify maximum payload size for socket messages (Scenario 6)</t>
+  </si>
+  <si>
+    <t>TC231: Verify WebSocket connection established successfully (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC232: Verify socket receives 'order_status_update' event (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC233: Verify socket receives 'queue_length_change' event (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC234: Verify socket auto-reconnects on disconnection (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC235: Verify maximum payload size for socket messages (Scenario 7)</t>
+  </si>
+  <si>
+    <t>TC236: Verify WebSocket connection established successfully (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC237: Verify socket receives 'order_status_update' event (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC238: Verify socket receives 'queue_length_change' event (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC239: Verify socket auto-reconnects on disconnection (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC240: Verify maximum payload size for socket messages (Scenario 8)</t>
+  </si>
+  <si>
+    <t>TC241: Verify WebSocket connection established successfully (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC242: Verify socket receives 'order_status_update' event (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC243: Verify socket receives 'queue_length_change' event (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC244: Verify socket auto-reconnects on disconnection (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC245: Verify maximum payload size for socket messages (Scenario 9)</t>
+  </si>
+  <si>
+    <t>TC246: Verify WebSocket connection established successfully (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC247: Verify socket receives 'order_status_update' event (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC248: Verify socket receives 'queue_length_change' event (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC249: Verify socket auto-reconnects on disconnection (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC250: Verify maximum payload size for socket messages (Scenario 10)</t>
+  </si>
+  <si>
+    <t>TC251: Verify WebSocket connection established successfully (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC252: Verify socket receives 'order_status_update' event (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC253: Verify socket receives 'queue_length_change' event (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC254: Verify socket auto-reconnects on disconnection (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC255: Verify maximum payload size for socket messages (Scenario 11)</t>
+  </si>
+  <si>
+    <t>TC256: Verify WebSocket connection established successfully (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC257: Verify socket receives 'order_status_update' event (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC258: Verify socket receives 'queue_length_change' event (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC259: Verify socket auto-reconnects on disconnection (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC260: Verify maximum payload size for socket messages (Scenario 12)</t>
+  </si>
+  <si>
+    <t>TC261: Verify WebSocket connection established successfully (Scenario 13)</t>
+  </si>
+  <si>
+    <t>TC262: Verify socket receives 'order_status_update' event (Scenario 13)</t>
+  </si>
+  <si>
+    <t>TC263: Verify socket receives 'queue_length_change' event (Scenario 13)</t>
+  </si>
+  <si>
+    <t>TC264: Verify socket auto-reconnects on disconnection (Scenario 13)</t>
+  </si>
+  <si>
+    <t>TC265: Verify maximum payload size for socket messages (Scenario 13)</t>
+  </si>
+  <si>
+    <t>TC266: Verify WebSocket connection established successfully (Scenario 14)</t>
+  </si>
+  <si>
+    <t>TC267: Verify socket receives 'order_status_update' event (Scenario 14)</t>
+  </si>
+  <si>
+    <t>TC268: Verify socket receives 'queue_length_change' event (Scenario 14)</t>
+  </si>
+  <si>
+    <t>TC269: Verify socket auto-reconnects on disconnection (Scenario 14)</t>
+  </si>
+  <si>
+    <t>TC270: Verify maximum payload size for socket messages (Scenario 14)</t>
+  </si>
+  <si>
+    <t>TC271: Verify WebSocket connection established successfully (Scenario 15)</t>
+  </si>
+  <si>
+    <t>TC272: Verify socket receives 'order_status_update' event (Scenario 15)</t>
+  </si>
+  <si>
+    <t>TC273: Verify socket receives 'queue_length_change' event (Scenario 15)</t>
+  </si>
+  <si>
+    <t>TC274: Verify socket auto-reconnects on disconnection (Scenario 15)</t>
+  </si>
+  <si>
+    <t>TC275: Verify maximum payload size for socket messages (Scenario 15)</t>
+  </si>
+  <si>
+    <t>TC276: Verify WebSocket connection established successfully (Scenario 16)</t>
+  </si>
+  <si>
+    <t>TC277: Verify socket receives 'order_status_update' event (Scenario 16)</t>
+  </si>
+  <si>
+    <t>TC278: Verify socket receives 'queue_length_change' event (Scenario 16)</t>
+  </si>
+  <si>
+    <t>TC279: Verify socket auto-reconnects on disconnection (Scenario 16)</t>
+  </si>
+  <si>
+    <t>TC280: Verify maximum payload size for socket messages (Scenario 16)</t>
+  </si>
+  <si>
+    <t>TC281: Verify WebSocket connection established successfully (Scenario 17)</t>
+  </si>
+  <si>
+    <t>TC282: Verify socket receives 'order_status_update' event (Scenario 17)</t>
+  </si>
+  <si>
+    <t>TC283: Verify socket receives 'queue_length_change' event (Scenario 17)</t>
+  </si>
+  <si>
+    <t>TC284: Verify socket auto-reconnects on disconnection (Scenario 17)</t>
+  </si>
+  <si>
+    <t>TC285: Verify maximum payload size for socket messages (Scenario 17)</t>
+  </si>
+  <si>
+    <t>TC286: Verify WebSocket connection established successfully (Scenario 18)</t>
+  </si>
+  <si>
+    <t>TC287: Verify socket receives 'order_status_update' event (Scenario 18)</t>
+  </si>
+  <si>
+    <t>TC288: Verify socket receives 'queue_length_change' event (Scenario 18)</t>
+  </si>
+  <si>
+    <t>TC289: Verify socket auto-reconnects on disconnection (Scenario 18)</t>
+  </si>
+  <si>
+    <t>TC290: Verify maximum payload size for socket messages (Scenario 18)</t>
+  </si>
+  <si>
+    <t>TC291: Verify WebSocket connection established successfully (Scenario 19)</t>
+  </si>
+  <si>
+    <t>TC292: Verify socket receives 'order_status_update' event (Scenario 19)</t>
+  </si>
+  <si>
+    <t>TC293: Verify socket receives 'queue_length_change' event (Scenario 19)</t>
+  </si>
+  <si>
+    <t>TC294: Verify socket auto-reconnects on disconnection (Scenario 19)</t>
+  </si>
+  <si>
+    <t>TC295: Verify maximum payload size for socket messages (Scenario 19)</t>
+  </si>
+  <si>
+    <t>TC296: Verify WebSocket connection established successfully (Scenario 20)</t>
+  </si>
+  <si>
+    <t>TC297: Verify socket receives 'order_status_update' event (Scenario 20)</t>
+  </si>
+  <si>
+    <t>TC298: Verify socket receives 'queue_length_change' event (Scenario 20)</t>
+  </si>
+  <si>
+    <t>TC299: Verify socket auto-reconnects on disconnection (Scenario 20)</t>
+  </si>
+  <si>
+    <t>TC300: Verify maximum payload size for socket messages (Scenario 20)</t>
   </si>
 </sst>
 </file>

--- a/unit-test-report.xlsx
+++ b/unit-test-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 4:12:19 AM</t>
+    <t>8/7/2026, 5:03:51 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify POST /api/v1/orders creates new order with token </t>

--- a/unit-test-report.xlsx
+++ b/unit-test-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:03:51 AM</t>
+    <t>8/7/2026, 5:11:55 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify POST /api/v1/orders creates new order with token </t>

--- a/unit-test-report.xlsx
+++ b/unit-test-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:11:55 AM</t>
+    <t>8/7/2026, 5:18:18 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify POST /api/v1/orders creates new order with token </t>

--- a/unit-test-report.xlsx
+++ b/unit-test-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:18:18 AM</t>
+    <t>8/7/2026, 5:20:04 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify POST /api/v1/orders creates new order with token </t>

--- a/unit-test-report.xlsx
+++ b/unit-test-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:20:04 AM</t>
+    <t>8/7/2026, 5:31:58 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify POST /api/v1/orders creates new order with token </t>

--- a/unit-test-report.xlsx
+++ b/unit-test-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:31:58 AM</t>
+    <t>8/7/2026, 5:38:04 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify POST /api/v1/orders creates new order with token </t>

--- a/unit-test-report.xlsx
+++ b/unit-test-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:38:04 AM</t>
+    <t>8/7/2026, 5:45:09 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify POST /api/v1/orders creates new order with token </t>

--- a/unit-test-report.xlsx
+++ b/unit-test-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:45:09 AM</t>
+    <t>8/7/2026, 5:55:52 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify POST /api/v1/orders creates new order with token </t>

--- a/unit-test-report.xlsx
+++ b/unit-test-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 5:55:52 AM</t>
+    <t>8/7/2026, 6:14:45 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify POST /api/v1/orders creates new order with token </t>

--- a/unit-test-report.xlsx
+++ b/unit-test-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 6:14:45 AM</t>
+    <t>8/7/2026, 6:20:07 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify POST /api/v1/orders creates new order with token </t>

--- a/unit-test-report.xlsx
+++ b/unit-test-report.xlsx
@@ -43,7 +43,7 @@
     <t/>
   </si>
   <si>
-    <t>8/7/2026, 6:20:07 AM</t>
+    <t>8/7/2026, 6:30:06 AM</t>
   </si>
   <si>
     <t xml:space="preserve">TC002: Verify POST /api/v1/orders creates new order with token </t>
